--- a/analysis/tables/pythia-410m.xlsx
+++ b/analysis/tables/pythia-410m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6429759828361528</v>
+        <v>0.4672292141942706</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1340901520472701</v>
+        <v>-0.0655060472114137</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.643x - 0.134</t>
+          <t>y = 0.467x - 0.066</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7006157380279142</v>
+        <v>0.7006157380279131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07034781690958251</v>
+        <v>0.07034781690958253</v>
       </c>
       <c r="I3" t="n">
-        <v>0.208546128668448</v>
+        <v>0.1402010944978641</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5088858307888826</v>
+        <v>0.4017231669828569</v>
       </c>
       <c r="K3" t="n">
         <v>0.09911605076223715</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9538258285793627</v>
+        <v>0.4662072281703645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03867663923445827</v>
+        <v>-0.06093213704864905</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.954x + 0.039</t>
+          <t>y = 0.466x - 0.061</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7586845960231761</v>
+        <v>0.7049694856586144</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0688903766546794</v>
+        <v>0.07023854444796132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04054895356740719</v>
+        <v>0.1306975382766541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.992502467813821</v>
+        <v>0.4052750911217154</v>
       </c>
       <c r="K4" t="n">
         <v>0.09911605076223715</v>
